--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_2_11.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_2_11.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>319650.2816502029</v>
+        <v>300771.3271433047</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2995127.424547405</v>
+        <v>3013503.893776014</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20355556.36745723</v>
+        <v>20373567.1449482</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4813076.283068547</v>
+        <v>4789718.594510994</v>
       </c>
     </row>
     <row r="11">
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -1132,16 +1132,16 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1208,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1256,19 +1256,19 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1293,19 +1293,19 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.27419204266741</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -1369,19 +1369,19 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9608114308426601</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1402,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1487,7 +1487,7 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1496,16 +1496,16 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1530,19 +1530,19 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2741920426674241</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1642,13 +1642,13 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1733,13 +1733,13 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -1773,13 +1773,13 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>23.55275130756091</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1794,10 +1794,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -1879,28 +1879,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U17" t="n">
-        <v>24.66239999999999</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1928,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>24.66239999999999</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1958,28 +1958,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2034,19 +2034,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="R19" t="n">
-        <v>22.02246762618612</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T19" t="n">
-        <v>28</v>
+        <v>22.44875936050941</v>
       </c>
       <c r="U19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2074,16 +2074,16 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2125,19 +2125,19 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V20" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
     </row>
     <row r="21">
@@ -2147,28 +2147,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>62.13484214871499</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
-        <v>89.69521348729178</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I21" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0.7465913262578567</v>
@@ -2198,13 +2198,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2286,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="W22" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2350,25 +2350,25 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>223.0958495641314</v>
+        <v>212.285385643442</v>
       </c>
       <c r="U23" t="n">
-        <v>102.2970636939287</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2387,19 +2387,19 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>172.7084989883157</v>
+        <v>145.4467082856156</v>
       </c>
       <c r="D24" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>15.11601384806353</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H24" t="n">
         <v>112.2354442364965</v>
@@ -2435,13 +2435,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2511,10 +2511,10 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="S25" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2560,10 +2560,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>94.41048699370604</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2590,16 +2590,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2621,25 +2621,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>62.82598119855365</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>137.3435171632106</v>
+        <v>69.03881051849277</v>
       </c>
       <c r="H27" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2678,13 +2678,13 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2779,13 +2779,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="D29" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -2797,7 +2797,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2836,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>212.2728</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="30">
@@ -2861,7 +2861,7 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -2873,16 +2873,16 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H30" t="n">
-        <v>67.77258988592654</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
         <v>171.6831711038378</v>
@@ -2915,10 +2915,10 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
-        <v>232.8005871494253</v>
+        <v>100.0376190809312</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -3019,22 +3019,22 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>215</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F32" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>179.3813007854552</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3076,7 +3076,7 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -3095,25 +3095,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>33.6917669883161</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>189.372</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3298,10 +3298,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -3310,19 +3310,19 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>179.3813007854552</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>62.4162677022923</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="36">
@@ -3332,31 +3332,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>74.16062543505005</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3383,22 +3383,22 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>101.030959446742</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
@@ -3490,19 +3490,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D38" t="n">
-        <v>189.3719999999999</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3584,13 +3584,13 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3617,22 +3617,22 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>65.3964057488777</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>215</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V39" t="n">
-        <v>215</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>4.580549094716531</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -3666,7 +3666,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -3702,7 +3702,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -3733,25 +3733,25 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="F41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>168.1945218604368</v>
+        <v>187.9840913941556</v>
       </c>
       <c r="I41" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -3818,19 +3818,19 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>17.27555404375957</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
-        <v>4.536356466206433</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3857,22 +3857,22 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -3894,7 +3894,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>47.02492433367365</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103.6392766348993</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>103.6392766348993</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>103.6392766348993</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>103.6392766348993</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>103.6392766348993</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>103.3623149756393</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>77.09968871301299</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>50.83706245038672</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>24.57443618776046</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>103.6392766348993</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>103.6392766348993</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>103.6392766348993</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>103.6392766348993</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>103.6392766348993</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>103.6392766348993</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>103.6392766348993</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>103.6392766348993</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>103.6392766348993</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>103.6392766348993</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>103.6392766348993</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>67.64575836914665</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>67.64575836914665</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>67.64575836914665</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>67.64575836914665</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>41.38313210652039</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>41.38313210652039</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>40.41261550970962</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>14.14998924708335</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>26.78000000000001</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>103.72303834074</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>77.46041207811371</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>51.19778581548745</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>28.18072336510073</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>53.92072336510073</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>79.66072336510072</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>26.78000000000001</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>74.98844370191262</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>74.98844370191262</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>74.98844370191262</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>74.98844370191262</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>74.98844370191262</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>74.98844370191262</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>74.98844370191262</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>51.19778581548745</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>24.93515955286119</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>28.18072336510073</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>53.92072336510073</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>79.66072336510072</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>101.2510699645389</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>74.98844370191262</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>74.98844370191262</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>74.98844370191262</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>74.98844370191262</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>74.98844370191262</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>74.98844370191262</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>74.98844370191262</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>74.98844370191262</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>74.98844370191262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K17" t="n">
-        <v>29.96</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L17" t="n">
-        <v>57.68</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="M17" t="n">
-        <v>85.40000000000001</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N17" t="n">
-        <v>112</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="O17" t="n">
-        <v>112</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R17" t="n">
-        <v>112</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="S17" t="n">
-        <v>112</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="T17" t="n">
-        <v>112</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="U17" t="n">
-        <v>87.08848484848485</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="V17" t="n">
-        <v>87.08848484848485</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="W17" t="n">
-        <v>58.80565656565657</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X17" t="n">
-        <v>30.52282828282829</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27.15151515151514</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C18" t="n">
-        <v>27.15151515151514</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D18" t="n">
-        <v>27.15151515151514</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E18" t="n">
-        <v>27.15151515151514</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F18" t="n">
-        <v>27.15151515151514</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G18" t="n">
-        <v>27.15151515151514</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L18" t="n">
-        <v>2.24</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M18" t="n">
-        <v>29.96</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="N18" t="n">
-        <v>57.68</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="O18" t="n">
-        <v>57.68</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P18" t="n">
-        <v>85.40000000000001</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R18" t="n">
-        <v>112</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="S18" t="n">
-        <v>112</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="T18" t="n">
-        <v>112</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="U18" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="V18" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="W18" t="n">
-        <v>83.71717171717171</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X18" t="n">
-        <v>55.43434343434343</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y18" t="n">
-        <v>27.15151515151514</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L19" t="n">
-        <v>29.55412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M19" t="n">
-        <v>57.27412500771297</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N19" t="n">
-        <v>84.99412500771297</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q19" t="n">
-        <v>109.3334016426122</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="R19" t="n">
-        <v>87.08848484848485</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="S19" t="n">
-        <v>58.80565656565657</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="T19" t="n">
-        <v>30.52282828282829</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="U19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="V19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="W19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>749.5830303030303</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C20" t="n">
-        <v>749.5830303030303</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D20" t="n">
-        <v>506.1486868686869</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E20" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F20" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R20" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S20" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T20" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U20" t="n">
-        <v>964</v>
+        <v>710.516763498309</v>
       </c>
       <c r="V20" t="n">
-        <v>749.5830303030303</v>
+        <v>710.516763498309</v>
       </c>
       <c r="W20" t="n">
-        <v>749.5830303030303</v>
+        <v>467.067986854209</v>
       </c>
       <c r="X20" t="n">
-        <v>749.5830303030303</v>
+        <v>223.6192102101089</v>
       </c>
       <c r="Y20" t="n">
-        <v>749.5830303030303</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>360.1724425458239</v>
+        <v>901.2946886937524</v>
       </c>
       <c r="C21" t="n">
-        <v>360.1724425458239</v>
+        <v>726.8416594126254</v>
       </c>
       <c r="D21" t="n">
-        <v>360.1724425458239</v>
+        <v>577.9072497513741</v>
       </c>
       <c r="E21" t="n">
-        <v>200.9349875403684</v>
+        <v>418.6697947459187</v>
       </c>
       <c r="F21" t="n">
-        <v>200.9349875403684</v>
+        <v>272.1352367728036</v>
       </c>
       <c r="G21" t="n">
-        <v>200.9349875403684</v>
+        <v>133.4044113554191</v>
       </c>
       <c r="H21" t="n">
-        <v>110.3337617956292</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I21" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L21" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="M21" t="n">
-        <v>383.2275600578374</v>
+        <v>383.2428491569326</v>
       </c>
       <c r="N21" t="n">
-        <v>473.3719638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O21" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P21" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T21" t="n">
-        <v>588.3960608094349</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U21" t="n">
-        <v>360.1724425458239</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V21" t="n">
-        <v>360.1724425458239</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W21" t="n">
-        <v>360.1724425458239</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X21" t="n">
-        <v>360.1724425458239</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y21" t="n">
-        <v>360.1724425458239</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V22" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R23" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S23" t="n">
-        <v>591.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T23" t="n">
-        <v>366.0447108019482</v>
+        <v>749.627473042513</v>
       </c>
       <c r="U23" t="n">
-        <v>262.7143434343434</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="V23" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="W23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>562.359037187058</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C24" t="n">
-        <v>387.906007905931</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D24" t="n">
-        <v>238.9715982446797</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E24" t="n">
-        <v>238.9715982446797</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F24" t="n">
-        <v>238.9715982446797</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G24" t="n">
-        <v>223.7028973880499</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H24" t="n">
-        <v>110.3337617956292</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I24" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L24" t="n">
-        <v>374.6006659261865</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M24" t="n">
-        <v>613.1906659261865</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N24" t="n">
-        <v>613.1906659261865</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O24" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P24" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S24" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T24" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U24" t="n">
-        <v>562.359037187058</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V24" t="n">
-        <v>562.359037187058</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W24" t="n">
-        <v>562.359037187058</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X24" t="n">
-        <v>562.359037187058</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y24" t="n">
-        <v>562.359037187058</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>749.5830303030303</v>
+        <v>358.0940480307835</v>
       </c>
       <c r="C26" t="n">
-        <v>506.1486868686869</v>
+        <v>358.0940480307835</v>
       </c>
       <c r="D26" t="n">
-        <v>262.7143434343434</v>
+        <v>358.0940480307835</v>
       </c>
       <c r="E26" t="n">
-        <v>19.28</v>
+        <v>358.0940480307835</v>
       </c>
       <c r="F26" t="n">
-        <v>19.28</v>
+        <v>358.0940480307835</v>
       </c>
       <c r="G26" t="n">
-        <v>19.28</v>
+        <v>358.0940480307835</v>
       </c>
       <c r="H26" t="n">
-        <v>19.28</v>
+        <v>114.6452713866835</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R26" t="n">
-        <v>964</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="S26" t="n">
-        <v>964</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="T26" t="n">
-        <v>964</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="U26" t="n">
-        <v>964</v>
+        <v>358.0940480307835</v>
       </c>
       <c r="V26" t="n">
-        <v>964</v>
+        <v>358.0940480307835</v>
       </c>
       <c r="W26" t="n">
-        <v>964</v>
+        <v>358.0940480307835</v>
       </c>
       <c r="X26" t="n">
-        <v>964</v>
+        <v>358.0940480307835</v>
       </c>
       <c r="Y26" t="n">
-        <v>964</v>
+        <v>358.0940480307835</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>900.5394129307539</v>
+        <v>89.01731535111452</v>
       </c>
       <c r="C27" t="n">
-        <v>726.0863836496269</v>
+        <v>89.01731535111452</v>
       </c>
       <c r="D27" t="n">
-        <v>577.1519739883756</v>
+        <v>89.01731535111452</v>
       </c>
       <c r="E27" t="n">
-        <v>417.9145189829202</v>
+        <v>89.01731535111452</v>
       </c>
       <c r="F27" t="n">
-        <v>271.3799610098052</v>
+        <v>89.01731535111452</v>
       </c>
       <c r="G27" t="n">
-        <v>132.6491355924207</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L27" t="n">
-        <v>19.28</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M27" t="n">
-        <v>257.87</v>
+        <v>417.4543050195419</v>
       </c>
       <c r="N27" t="n">
-        <v>496.46</v>
+        <v>656.0584510084244</v>
       </c>
       <c r="O27" t="n">
-        <v>735.0500000000001</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P27" t="n">
-        <v>917.693477613351</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U27" t="n">
-        <v>964</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V27" t="n">
-        <v>964</v>
+        <v>500.6814290152826</v>
       </c>
       <c r="W27" t="n">
-        <v>964</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="X27" t="n">
-        <v>964</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="Y27" t="n">
-        <v>964</v>
+        <v>257.2326523711826</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S28" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T28" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U28" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V28" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W28" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X28" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y28" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>506.1486868686869</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="C29" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D29" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E29" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F29" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G29" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U29" t="n">
-        <v>749.5830303030303</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="V29" t="n">
-        <v>749.5830303030303</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="W29" t="n">
-        <v>749.5830303030303</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X29" t="n">
-        <v>749.5830303030303</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y29" t="n">
-        <v>749.5830303030303</v>
+        <v>477.1596022224361</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>353.2439525776921</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="C30" t="n">
-        <v>178.7909232965651</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="D30" t="n">
-        <v>178.7909232965651</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="E30" t="n">
-        <v>178.7909232965651</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="F30" t="n">
-        <v>178.7909232965651</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="G30" t="n">
-        <v>178.7909232965651</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H30" t="n">
-        <v>110.3337617956292</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I30" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L30" t="n">
-        <v>374.6006659261865</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="M30" t="n">
-        <v>542.7665223866492</v>
+        <v>383.2428491569326</v>
       </c>
       <c r="N30" t="n">
-        <v>542.7665223866492</v>
+        <v>621.8469951458151</v>
       </c>
       <c r="O30" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P30" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S30" t="n">
-        <v>790.5826554506689</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T30" t="n">
-        <v>588.3960608094349</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U30" t="n">
-        <v>588.3960608094349</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="V30" t="n">
-        <v>353.2439525776921</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="W30" t="n">
-        <v>353.2439525776921</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="X30" t="n">
-        <v>353.2439525776921</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="Y30" t="n">
-        <v>353.2439525776921</v>
+        <v>158.0119685275972</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>849.9083846317729</v>
+        <v>710.516763498309</v>
       </c>
       <c r="C32" t="n">
-        <v>632.7366674600557</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D32" t="n">
-        <v>632.7366674600557</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E32" t="n">
-        <v>415.5649502883385</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F32" t="n">
-        <v>198.3932331166214</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G32" t="n">
-        <v>198.3932331166214</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K32" t="n">
-        <v>120.2150059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L32" t="n">
-        <v>202.4404723580617</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M32" t="n">
-        <v>415.2904723580617</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N32" t="n">
-        <v>621.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O32" t="n">
-        <v>770.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P32" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q32" t="n">
-        <v>849.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R32" t="n">
-        <v>849.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S32" t="n">
-        <v>849.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T32" t="n">
-        <v>849.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U32" t="n">
-        <v>849.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V32" t="n">
-        <v>849.9083846317729</v>
+        <v>710.516763498309</v>
       </c>
       <c r="W32" t="n">
-        <v>849.9083846317729</v>
+        <v>710.516763498309</v>
       </c>
       <c r="X32" t="n">
-        <v>849.9083846317729</v>
+        <v>710.516763498309</v>
       </c>
       <c r="Y32" t="n">
-        <v>849.9083846317729</v>
+        <v>710.516763498309</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17.2</v>
+        <v>795.8418184905681</v>
       </c>
       <c r="C33" t="n">
-        <v>17.2</v>
+        <v>621.3887892094411</v>
       </c>
       <c r="D33" t="n">
-        <v>17.2</v>
+        <v>472.4543795481899</v>
       </c>
       <c r="E33" t="n">
-        <v>17.2</v>
+        <v>313.2169245427344</v>
       </c>
       <c r="F33" t="n">
-        <v>17.2</v>
+        <v>166.6823665696193</v>
       </c>
       <c r="G33" t="n">
-        <v>17.2</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="H33" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I33" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J33" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K33" t="n">
-        <v>142.5575600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L33" t="n">
-        <v>142.5575600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="M33" t="n">
-        <v>355.4075600578374</v>
+        <v>383.2428491569326</v>
       </c>
       <c r="N33" t="n">
-        <v>464.5065223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O33" t="n">
-        <v>677.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P33" t="n">
-        <v>860</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q33" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R33" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S33" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T33" t="n">
-        <v>668.7151515151515</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U33" t="n">
-        <v>451.5434343434343</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V33" t="n">
-        <v>234.3717171717172</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W33" t="n">
-        <v>17.2</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X33" t="n">
-        <v>17.2</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y33" t="n">
-        <v>17.2</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>725.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C34" t="n">
-        <v>725.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D34" t="n">
-        <v>725.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E34" t="n">
-        <v>725.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F34" t="n">
-        <v>725.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G34" t="n">
-        <v>725.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H34" t="n">
-        <v>725.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I34" t="n">
-        <v>725.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J34" t="n">
-        <v>725.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K34" t="n">
-        <v>725.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L34" t="n">
-        <v>752.7818345174422</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M34" t="n">
-        <v>791.9698727096644</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N34" t="n">
-        <v>835.6607233651007</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O34" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P34" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q34" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R34" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S34" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T34" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U34" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V34" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W34" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X34" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y34" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>451.5434343434343</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C35" t="n">
-        <v>234.3717171717172</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D35" t="n">
-        <v>234.3717171717172</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E35" t="n">
-        <v>234.3717171717172</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F35" t="n">
-        <v>234.3717171717172</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G35" t="n">
-        <v>234.3717171717172</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K35" t="n">
-        <v>120.2150059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L35" t="n">
-        <v>300.290857495581</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M35" t="n">
-        <v>513.1408574955809</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N35" t="n">
-        <v>621.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O35" t="n">
-        <v>770.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P35" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q35" t="n">
-        <v>849.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R35" t="n">
-        <v>849.9083846317729</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="S35" t="n">
-        <v>849.9083846317729</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="T35" t="n">
-        <v>849.9083846317729</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="U35" t="n">
-        <v>668.7151515151515</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="V35" t="n">
-        <v>668.7151515151515</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W35" t="n">
-        <v>668.7151515151515</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="X35" t="n">
-        <v>668.7151515151515</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="Y35" t="n">
-        <v>668.7151515151515</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>860</v>
+        <v>110.334904905842</v>
       </c>
       <c r="C36" t="n">
-        <v>685.546970718873</v>
+        <v>110.334904905842</v>
       </c>
       <c r="D36" t="n">
-        <v>536.6125610576217</v>
+        <v>110.334904905842</v>
       </c>
       <c r="E36" t="n">
-        <v>377.3751060521662</v>
+        <v>110.334904905842</v>
       </c>
       <c r="F36" t="n">
-        <v>230.8405480790512</v>
+        <v>110.334904905842</v>
       </c>
       <c r="G36" t="n">
-        <v>92.10972266166672</v>
+        <v>110.334904905842</v>
       </c>
       <c r="H36" t="n">
-        <v>17.2</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I36" t="n">
-        <v>17.2</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K36" t="n">
-        <v>17.2</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L36" t="n">
-        <v>230.05</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="M36" t="n">
-        <v>442.9</v>
+        <v>383.2428491569326</v>
       </c>
       <c r="N36" t="n">
-        <v>647.15</v>
+        <v>621.8469951458151</v>
       </c>
       <c r="O36" t="n">
-        <v>860</v>
+        <v>860.4511411346975</v>
       </c>
       <c r="P36" t="n">
-        <v>860</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q36" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R36" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S36" t="n">
-        <v>860</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T36" t="n">
-        <v>860</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="U36" t="n">
-        <v>860</v>
+        <v>588.4532163200711</v>
       </c>
       <c r="V36" t="n">
-        <v>860</v>
+        <v>486.4017421314428</v>
       </c>
       <c r="W36" t="n">
-        <v>860</v>
+        <v>486.4017421314428</v>
       </c>
       <c r="X36" t="n">
-        <v>860</v>
+        <v>278.55024192591</v>
       </c>
       <c r="Y36" t="n">
-        <v>860</v>
+        <v>278.55024192591</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>725.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C37" t="n">
-        <v>725.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D37" t="n">
-        <v>725.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E37" t="n">
-        <v>725.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F37" t="n">
-        <v>725.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G37" t="n">
-        <v>725.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H37" t="n">
-        <v>725.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I37" t="n">
-        <v>725.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J37" t="n">
-        <v>725.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K37" t="n">
-        <v>725.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L37" t="n">
-        <v>752.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M37" t="n">
-        <v>791.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N37" t="n">
-        <v>835.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O37" t="n">
-        <v>860</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P37" t="n">
-        <v>860</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q37" t="n">
-        <v>860</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R37" t="n">
-        <v>860</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S37" t="n">
-        <v>860</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T37" t="n">
-        <v>860</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U37" t="n">
-        <v>860</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V37" t="n">
-        <v>725.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W37" t="n">
-        <v>725.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X37" t="n">
-        <v>725.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y37" t="n">
-        <v>725.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>425.6565656565656</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C38" t="n">
-        <v>208.4848484848484</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="D38" t="n">
-        <v>17.2</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="E38" t="n">
-        <v>17.2</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F38" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G38" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H38" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I38" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J38" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K38" t="n">
-        <v>120.2150059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L38" t="n">
-        <v>300.290857495581</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M38" t="n">
-        <v>513.1408574955809</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N38" t="n">
-        <v>718.9953797028202</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O38" t="n">
-        <v>770.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P38" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q38" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R38" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S38" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T38" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U38" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V38" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W38" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X38" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y38" t="n">
-        <v>642.8282828282828</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>359.5995901526487</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C39" t="n">
-        <v>359.5995901526487</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D39" t="n">
-        <v>359.5995901526487</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E39" t="n">
-        <v>359.5995901526487</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F39" t="n">
-        <v>359.5995901526487</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G39" t="n">
-        <v>220.8687647352642</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H39" t="n">
-        <v>107.4996291428435</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I39" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J39" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K39" t="n">
-        <v>142.5575600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L39" t="n">
-        <v>142.5575600578374</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M39" t="n">
-        <v>355.4075600578374</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N39" t="n">
-        <v>568.2575600578374</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O39" t="n">
-        <v>781.1075600578374</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P39" t="n">
-        <v>860</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q39" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R39" t="n">
-        <v>860</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S39" t="n">
-        <v>793.9430244960831</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T39" t="n">
-        <v>793.9430244960831</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U39" t="n">
-        <v>576.7713073243659</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="V39" t="n">
-        <v>359.5995901526487</v>
+        <v>23.90796037760316</v>
       </c>
       <c r="W39" t="n">
-        <v>359.5995901526487</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X39" t="n">
-        <v>359.5995901526487</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y39" t="n">
-        <v>359.5995901526487</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L40" t="n">
-        <v>44.51412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M40" t="n">
-        <v>83.70216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N40" t="n">
-        <v>127.3930138553715</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>841.9083846317729</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="C41" t="n">
-        <v>841.9083846317729</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="D41" t="n">
-        <v>841.9083846317729</v>
+        <v>422.536925949487</v>
       </c>
       <c r="E41" t="n">
-        <v>841.9083846317729</v>
+        <v>206.9568616895446</v>
       </c>
       <c r="F41" t="n">
-        <v>626.7568694802578</v>
+        <v>206.9568616895446</v>
       </c>
       <c r="G41" t="n">
-        <v>411.6053543287427</v>
+        <v>206.9568616895446</v>
       </c>
       <c r="H41" t="n">
-        <v>241.711897904059</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I41" t="n">
-        <v>29.10998924708335</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K41" t="n">
-        <v>120.0550059109223</v>
+        <v>120.0889470003098</v>
       </c>
       <c r="L41" t="n">
-        <v>196.4204723580617</v>
+        <v>300.1647985849684</v>
       </c>
       <c r="M41" t="n">
-        <v>407.2904723580617</v>
+        <v>511.4548195661379</v>
       </c>
       <c r="N41" t="n">
-        <v>613.144994565301</v>
+        <v>614.8420490346726</v>
       </c>
       <c r="O41" t="n">
-        <v>762.339944707949</v>
+        <v>764.0369991773207</v>
       </c>
       <c r="P41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="U41" t="n">
-        <v>841.9083846317729</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="V41" t="n">
-        <v>841.9083846317729</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="W41" t="n">
-        <v>841.9083846317729</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="X41" t="n">
-        <v>841.9083846317729</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="Y41" t="n">
-        <v>841.9083846317729</v>
+        <v>638.1169902094293</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>112.6759400443226</v>
+        <v>376.9235858316923</v>
       </c>
       <c r="C42" t="n">
-        <v>112.6759400443226</v>
+        <v>376.9235858316923</v>
       </c>
       <c r="D42" t="n">
-        <v>112.6759400443226</v>
+        <v>376.9235858316923</v>
       </c>
       <c r="E42" t="n">
-        <v>112.6759400443226</v>
+        <v>376.9235858316923</v>
       </c>
       <c r="F42" t="n">
-        <v>112.6759400443226</v>
+        <v>359.4735312420361</v>
       </c>
       <c r="G42" t="n">
-        <v>112.6759400443226</v>
+        <v>220.7427058246516</v>
       </c>
       <c r="H42" t="n">
-        <v>108.0937617956292</v>
+        <v>107.3735702322309</v>
       </c>
       <c r="I42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L42" t="n">
-        <v>17.04</v>
+        <v>228.3639620705569</v>
       </c>
       <c r="M42" t="n">
-        <v>227.91</v>
+        <v>439.6539830517264</v>
       </c>
       <c r="N42" t="n">
-        <v>438.78</v>
+        <v>642.4070334882022</v>
       </c>
       <c r="O42" t="n">
-        <v>649.65</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="P42" t="n">
-        <v>832.2934776133509</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R42" t="n">
-        <v>750.8304705528857</v>
+        <v>752.5275250222574</v>
       </c>
       <c r="S42" t="n">
-        <v>750.8304705528857</v>
+        <v>579.1101804729262</v>
       </c>
       <c r="T42" t="n">
-        <v>750.8304705528857</v>
+        <v>376.9235858316923</v>
       </c>
       <c r="U42" t="n">
-        <v>750.8304705528857</v>
+        <v>376.9235858316923</v>
       </c>
       <c r="V42" t="n">
-        <v>535.6789554013706</v>
+        <v>376.9235858316923</v>
       </c>
       <c r="W42" t="n">
-        <v>320.5274402498554</v>
+        <v>376.9235858316923</v>
       </c>
       <c r="X42" t="n">
-        <v>112.6759400443226</v>
+        <v>376.9235858316923</v>
       </c>
       <c r="Y42" t="n">
-        <v>112.6759400443226</v>
+        <v>376.9235858316923</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.04</v>
+        <v>64.57386465875476</v>
       </c>
       <c r="C43" t="n">
-        <v>17.04</v>
+        <v>64.57386465875476</v>
       </c>
       <c r="D43" t="n">
-        <v>17.04</v>
+        <v>64.57386465875476</v>
       </c>
       <c r="E43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L43" t="n">
-        <v>44.35412500771298</v>
+        <v>44.38806609710041</v>
       </c>
       <c r="M43" t="n">
-        <v>83.54216319993516</v>
+        <v>83.57610428932259</v>
       </c>
       <c r="N43" t="n">
-        <v>127.2330138553715</v>
+        <v>127.2669549447589</v>
       </c>
       <c r="O43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="P43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="Q43" t="n">
-        <v>151.5722904902707</v>
+        <v>64.57386465875476</v>
       </c>
       <c r="R43" t="n">
-        <v>151.5722904902707</v>
+        <v>64.57386465875476</v>
       </c>
       <c r="S43" t="n">
-        <v>151.5722904902707</v>
+        <v>64.57386465875476</v>
       </c>
       <c r="T43" t="n">
-        <v>151.5722904902707</v>
+        <v>64.57386465875476</v>
       </c>
       <c r="U43" t="n">
-        <v>151.5722904902707</v>
+        <v>64.57386465875476</v>
       </c>
       <c r="V43" t="n">
-        <v>151.5722904902707</v>
+        <v>64.57386465875476</v>
       </c>
       <c r="W43" t="n">
-        <v>151.5722904902707</v>
+        <v>64.57386465875476</v>
       </c>
       <c r="X43" t="n">
-        <v>151.5722904902707</v>
+        <v>64.57386465875476</v>
       </c>
       <c r="Y43" t="n">
-        <v>17.04</v>
+        <v>64.57386465875476</v>
       </c>
     </row>
     <row r="44">
@@ -8433,10 +8433,10 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>246.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L8" t="n">
-        <v>260.7159099194822</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M8" t="n">
         <v>230.3462332272727</v>
@@ -8445,10 +8445,10 @@
         <v>229.4130635965909</v>
       </c>
       <c r="O8" t="n">
-        <v>256.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P8" t="n">
-        <v>257.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8512,13 +8512,13 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K9" t="n">
-        <v>163.841438974359</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L9" t="n">
-        <v>164.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
-        <v>167.0835288715133</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
         <v>131.3417120833333</v>
@@ -8530,7 +8530,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8594,16 +8594,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M10" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N10" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O10" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P10" t="n">
         <v>135.0065633140411</v>
@@ -8673,19 +8673,19 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L11" t="n">
-        <v>261.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M11" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N11" t="n">
-        <v>254.3625585460859</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
-        <v>256.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P11" t="n">
-        <v>257.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q11" t="n">
         <v>212.3149906599047</v>
@@ -8755,16 +8755,16 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M12" t="n">
-        <v>167.0835288715133</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N12" t="n">
-        <v>157.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O12" t="n">
-        <v>168.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>159.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q12" t="n">
         <v>139.9817740860215</v>
@@ -8831,16 +8831,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M13" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N13" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O13" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P13" t="n">
         <v>135.0065633140411</v>
@@ -8910,19 +8910,19 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L14" t="n">
-        <v>261.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M14" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N14" t="n">
-        <v>255.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
-        <v>256.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P14" t="n">
-        <v>256.1824907047645</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q14" t="n">
         <v>212.3149906599047</v>
@@ -8992,19 +8992,19 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M15" t="n">
-        <v>167.0835288715133</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N15" t="n">
-        <v>157.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>159.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9068,16 +9068,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M16" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N16" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O16" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P16" t="n">
         <v>135.0065633140411</v>
@@ -9144,22 +9144,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>248.0898510449805</v>
+        <v>247.6798763052967</v>
       </c>
       <c r="L17" t="n">
-        <v>263.7664149699872</v>
+        <v>263.3564402303034</v>
       </c>
       <c r="M17" t="n">
-        <v>258.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N17" t="n">
-        <v>256.2817504652778</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O17" t="n">
-        <v>230.0982114216867</v>
+        <v>256.5734881866366</v>
       </c>
       <c r="P17" t="n">
-        <v>231.2329957552695</v>
+        <v>258.8230210155857</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9226,22 +9226,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L18" t="n">
-        <v>138.5543797798742</v>
+        <v>166.1444050401903</v>
       </c>
       <c r="M18" t="n">
-        <v>170.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N18" t="n">
-        <v>159.3417120833333</v>
+        <v>157.8169888482831</v>
       </c>
       <c r="O18" t="n">
-        <v>142.5962444444444</v>
+        <v>170.1862697047606</v>
       </c>
       <c r="P18" t="n">
-        <v>161.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
-        <v>166.8504609547084</v>
+        <v>167.5717993463377</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9308,10 +9308,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M19" t="n">
-        <v>166.9257839476051</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N19" t="n">
-        <v>155.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O19" t="n">
         <v>163.0416663658825</v>
@@ -9384,7 +9384,7 @@
         <v>324.1454125711647</v>
       </c>
       <c r="L20" t="n">
-        <v>417.6612145504504</v>
+        <v>417.6612145504505</v>
       </c>
       <c r="M20" t="n">
         <v>449.5135334928325</v>
@@ -9396,7 +9396,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P20" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q20" t="n">
         <v>212.3149906599047</v>
@@ -9466,19 +9466,19 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M21" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>222.3966654323053</v>
+        <v>292.5201795090609</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P21" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q21" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9697,25 +9697,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L24" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M24" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N24" t="n">
-        <v>131.3417120833333</v>
+        <v>349.0484638974528</v>
       </c>
       <c r="O24" t="n">
-        <v>312.4607459196593</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P24" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q24" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9855,7 +9855,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L26" t="n">
         <v>417.6612145504504</v>
@@ -9934,25 +9934,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L27" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M27" t="n">
-        <v>383.1340339220183</v>
+        <v>185.4193833999402</v>
       </c>
       <c r="N27" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O27" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P27" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q27" t="n">
-        <v>186.7560391230408</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10101,7 +10101,7 @@
         <v>449.5135334928325</v>
       </c>
       <c r="N29" t="n">
-        <v>437.2903462297383</v>
+        <v>437.3469244119842</v>
       </c>
       <c r="O29" t="n">
         <v>380.8001812627454</v>
@@ -10174,22 +10174,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L30" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
-        <v>311.9985353972331</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N30" t="n">
-        <v>131.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>233.6791982203443</v>
       </c>
       <c r="P30" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q30" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10332,10 +10332,10 @@
         <v>324.1454125711647</v>
       </c>
       <c r="L32" t="n">
-        <v>318.8224416842694</v>
+        <v>417.6612145504504</v>
       </c>
       <c r="M32" t="n">
-        <v>445.3462332272727</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N32" t="n">
         <v>437.3469244119842</v>
@@ -10414,19 +10414,19 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M33" t="n">
-        <v>357.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N33" t="n">
-        <v>241.5426841326382</v>
+        <v>222.4246658592332</v>
       </c>
       <c r="O33" t="n">
-        <v>357.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P33" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q33" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10572,10 +10572,10 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M35" t="n">
-        <v>445.3462332272727</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N35" t="n">
-        <v>338.5081515458031</v>
+        <v>437.3469244119842</v>
       </c>
       <c r="O35" t="n">
         <v>380.8001812627454</v>
@@ -10645,25 +10645,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L36" t="n">
-        <v>353.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M36" t="n">
-        <v>357.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N36" t="n">
-        <v>337.6548433964646</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O36" t="n">
-        <v>357.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P36" t="n">
-        <v>133.9744074143302</v>
+        <v>168.5314335381781</v>
       </c>
       <c r="Q36" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10803,19 +10803,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>324.1454125711647</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L38" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M38" t="n">
-        <v>445.3462332272727</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N38" t="n">
         <v>437.3469244119842</v>
       </c>
       <c r="O38" t="n">
-        <v>281.9614083965644</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P38" t="n">
         <v>321.7987081714826</v>
@@ -10882,25 +10882,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K39" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M39" t="n">
-        <v>357.1340339220183</v>
+        <v>368.5691090902119</v>
       </c>
       <c r="N39" t="n">
-        <v>346.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>357.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P39" t="n">
-        <v>213.6637406892419</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q39" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -11043,13 +11043,13 @@
         <v>324.1454125711647</v>
       </c>
       <c r="L41" t="n">
-        <v>312.9032497650775</v>
+        <v>417.6612145504504</v>
       </c>
       <c r="M41" t="n">
-        <v>443.3462332272727</v>
+        <v>443.7704968446156</v>
       </c>
       <c r="N41" t="n">
-        <v>437.3469244119842</v>
+        <v>333.8446085143028</v>
       </c>
       <c r="O41" t="n">
         <v>380.8001812627454</v>
@@ -11122,22 +11122,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
-        <v>138.5543797798742</v>
+        <v>351.9786433972171</v>
       </c>
       <c r="M42" t="n">
-        <v>355.1340339220183</v>
+        <v>355.5582975393612</v>
       </c>
       <c r="N42" t="n">
-        <v>344.3417120833333</v>
+        <v>336.1427731302785</v>
       </c>
       <c r="O42" t="n">
-        <v>355.5962444444444</v>
+        <v>356.0205080617874</v>
       </c>
       <c r="P42" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q42" t="n">
-        <v>159.887352254354</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -22978,7 +22978,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>359.8330416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C8" t="n">
         <v>365.2728917710076</v>
@@ -22990,16 +22990,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F8" t="n">
-        <v>380.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
         <v>415.302737515135</v>
       </c>
       <c r="H8" t="n">
-        <v>313.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I8" t="n">
-        <v>184.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J8" t="n">
         <v>11.94928935461252</v>
@@ -23066,7 +23066,7 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E9" t="n">
-        <v>134.7442804554009</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F9" t="n">
         <v>145.0692123933839</v>
@@ -23114,19 +23114,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U9" t="n">
-        <v>199.9413820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V9" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W9" t="n">
-        <v>225.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X9" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y9" t="n">
-        <v>179.6826957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="10">
@@ -23151,19 +23151,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.7167873157914</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H10" t="n">
-        <v>136.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I10" t="n">
-        <v>129.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J10" t="n">
-        <v>67.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23215,7 +23215,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>356.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C11" t="n">
         <v>365.2728917710076</v>
@@ -23227,19 +23227,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F11" t="n">
-        <v>380.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
         <v>415.302737515135</v>
       </c>
       <c r="H11" t="n">
-        <v>338.5139906849245</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I11" t="n">
-        <v>184.4758895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -23260,7 +23260,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
         <v>149.8691179411497</v>
@@ -23345,7 +23345,7 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S12" t="n">
-        <v>148.7823711038378</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T12" t="n">
         <v>200.1647286948216</v>
@@ -23354,16 +23354,16 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V12" t="n">
-        <v>206.8005871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W12" t="n">
         <v>251.6949831609196</v>
       </c>
       <c r="X12" t="n">
-        <v>179.7729852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y12" t="n">
-        <v>179.6826957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="13">
@@ -23388,19 +23388,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.7167873157913</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H13" t="n">
-        <v>136.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I13" t="n">
-        <v>129.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J13" t="n">
-        <v>67.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23452,7 +23452,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>359.8330416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C14" t="n">
         <v>365.2728917710076</v>
@@ -23500,13 +23500,13 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
-        <v>123.8691179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S14" t="n">
-        <v>183.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T14" t="n">
-        <v>197.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U14" t="n">
         <v>251.3456529078365</v>
@@ -23537,7 +23537,7 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D15" t="n">
-        <v>124.5442655646388</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E15" t="n">
         <v>157.6450804554009</v>
@@ -23591,13 +23591,13 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V15" t="n">
-        <v>206.8005871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W15" t="n">
-        <v>225.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X15" t="n">
-        <v>179.7729852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y15" t="n">
         <v>205.6826957773044</v>
@@ -23631,13 +23631,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I16" t="n">
-        <v>131.8977236196974</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J16" t="n">
-        <v>67.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -23652,10 +23652,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
-        <v>60.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R16" t="n">
         <v>177.2933913771695</v>
@@ -23737,28 +23737,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>149.8691179411497</v>
+        <v>125.5678236918632</v>
       </c>
       <c r="S17" t="n">
-        <v>209.0200695862453</v>
+        <v>181.4300443259292</v>
       </c>
       <c r="T17" t="n">
-        <v>223.0958495641314</v>
+        <v>195.5058243038152</v>
       </c>
       <c r="U17" t="n">
-        <v>226.6832529078365</v>
+        <v>223.7556276475204</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W17" t="n">
-        <v>321.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X17" t="n">
-        <v>341.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y17" t="n">
-        <v>358.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="18">
@@ -23786,7 +23786,7 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H18" t="n">
-        <v>87.57304423649647</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I18" t="n">
         <v>89.39663285141508</v>
@@ -23816,28 +23816,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>100.1578341526431</v>
+        <v>72.56780889232699</v>
       </c>
       <c r="S18" t="n">
-        <v>171.6831711038378</v>
+        <v>144.0931458435217</v>
       </c>
       <c r="T18" t="n">
-        <v>200.1647286948216</v>
+        <v>172.5747034345055</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9413820809748</v>
+        <v>201.6400878316884</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W18" t="n">
-        <v>223.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X18" t="n">
-        <v>177.7729852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y18" t="n">
-        <v>177.6826957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="19">
@@ -23892,19 +23892,19 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q19" t="n">
-        <v>86.16204325169439</v>
+        <v>58.57201799137825</v>
       </c>
       <c r="R19" t="n">
-        <v>155.2709237509834</v>
+        <v>149.7033661168533</v>
       </c>
       <c r="S19" t="n">
-        <v>196.0165980369723</v>
+        <v>196.4265727766561</v>
       </c>
       <c r="T19" t="n">
-        <v>199.9455894282815</v>
+        <v>205.4968300677721</v>
       </c>
       <c r="U19" t="n">
-        <v>258.3190293564909</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23932,16 +23932,16 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D20" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E20" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F20" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H20" t="n">
         <v>339.4748021157671</v>
@@ -23971,7 +23971,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>149.8691179411497</v>
@@ -23983,19 +23983,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U20" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V20" t="n">
-        <v>115.4794584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X20" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y20" t="n">
-        <v>386.2379386560536</v>
+        <v>183.9432522271564</v>
       </c>
     </row>
     <row r="21">
@@ -24005,28 +24005,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>166.5331836498673</v>
+        <v>104.3983415011523</v>
       </c>
       <c r="C21" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>22.54023074920467</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -24056,13 +24056,13 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24144,10 +24144,10 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V22" t="n">
-        <v>252.137643323828</v>
+        <v>118.95067573846</v>
       </c>
       <c r="W22" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X22" t="n">
         <v>225.7096553890372</v>
@@ -24208,25 +24208,25 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>10.81046392068936</v>
       </c>
       <c r="U23" t="n">
-        <v>149.0485892139078</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V23" t="n">
-        <v>86.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W23" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X23" t="n">
         <v>369.731100678469</v>
@@ -24245,19 +24245,19 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>27.26179070270013</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>122.2275033151471</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -24293,13 +24293,13 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24369,10 +24369,10 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>177.2933913771695</v>
+        <v>44.10642379180146</v>
       </c>
       <c r="S25" t="n">
-        <v>90.82963045160423</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T25" t="n">
         <v>227.9455894282815</v>
@@ -24400,16 +24400,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>170.4610416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C26" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D26" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E26" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F26" t="n">
         <v>406.8760457417114</v>
@@ -24418,10 +24418,10 @@
         <v>415.302737515135</v>
       </c>
       <c r="H26" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I26" t="n">
-        <v>210.4758895704059</v>
+        <v>116.0654025766999</v>
       </c>
       <c r="J26" t="n">
         <v>11.94928935461252</v>
@@ -24448,16 +24448,16 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24479,25 +24479,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>103.7072024513137</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>68.30470664471787</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I27" t="n">
         <v>89.39663285141508</v>
@@ -24536,13 +24536,13 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X27" t="n">
         <v>205.7729852034775</v>
@@ -24558,7 +24558,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>179.8319801819373</v>
+        <v>46.64501259656927</v>
       </c>
       <c r="C28" t="n">
         <v>167.2468210986278</v>
@@ -24609,7 +24609,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S28" t="n">
-        <v>90.82963045160423</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T28" t="n">
         <v>227.9455894282815</v>
@@ -24637,13 +24637,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C29" t="n">
-        <v>365.2728917710076</v>
+        <v>152.9875061275654</v>
       </c>
       <c r="D29" t="n">
-        <v>113.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E29" t="n">
         <v>381.9303700722618</v>
@@ -24655,7 +24655,7 @@
         <v>415.302737515135</v>
       </c>
       <c r="H29" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I29" t="n">
         <v>210.4758895704059</v>
@@ -24694,7 +24694,7 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
-        <v>39.07285290783653</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24706,7 +24706,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y29" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="30">
@@ -24719,7 +24719,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D30" t="n">
         <v>147.4450655646388</v>
@@ -24731,16 +24731,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>44.46285435056993</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -24764,7 +24764,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -24773,10 +24773,10 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>132.7629680684941</v>
       </c>
       <c r="W30" t="n">
         <v>251.6949831609196</v>
@@ -24877,22 +24877,22 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C32" t="n">
-        <v>150.2728917710076</v>
+        <v>162.9782053421103</v>
       </c>
       <c r="D32" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E32" t="n">
-        <v>166.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F32" t="n">
-        <v>191.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G32" t="n">
         <v>415.302737515135</v>
       </c>
       <c r="H32" t="n">
-        <v>160.093501330312</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I32" t="n">
         <v>210.4758895704059</v>
@@ -24934,7 +24934,7 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V32" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W32" t="n">
         <v>349.240968717413</v>
@@ -24953,25 +24953,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3435171632106</v>
+        <v>103.6517501748945</v>
       </c>
       <c r="H33" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>89.39663285141508</v>
@@ -25007,16 +25007,16 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
-        <v>10.79272869482165</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>10.94138208097482</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
-        <v>17.80058714942527</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>36.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X33" t="n">
         <v>205.7729852034775</v>
@@ -25032,10 +25032,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>46.64501259656927</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C34" t="n">
-        <v>167.2468210986278</v>
+        <v>34.05985351325984</v>
       </c>
       <c r="D34" t="n">
         <v>148.6154730182124</v>
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>167.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C35" t="n">
-        <v>150.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D35" t="n">
         <v>354.683041620683</v>
@@ -25129,7 +25129,7 @@
         <v>415.302737515135</v>
       </c>
       <c r="H35" t="n">
-        <v>124.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I35" t="n">
         <v>210.4758895704059</v>
@@ -25156,10 +25156,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>209.0200695862453</v>
@@ -25168,19 +25168,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U35" t="n">
-        <v>71.96435212238131</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V35" t="n">
-        <v>327.7522584701349</v>
+        <v>265.3359907678426</v>
       </c>
       <c r="W35" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X35" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y35" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="36">
@@ -25190,31 +25190,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H36" t="n">
-        <v>38.07481880144641</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I36" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -25241,22 +25241,22 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
-        <v>232.8005871494253</v>
+        <v>131.7696277026833</v>
       </c>
       <c r="W36" t="n">
         <v>251.6949831609196</v>
       </c>
       <c r="X36" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>205.6826957773044</v>
@@ -25317,7 +25317,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R37" t="n">
-        <v>177.2933913771695</v>
+        <v>44.10642379180146</v>
       </c>
       <c r="S37" t="n">
         <v>224.0165980369723</v>
@@ -25329,7 +25329,7 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V37" t="n">
-        <v>118.95067573846</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W37" t="n">
         <v>286.522998336591</v>
@@ -25348,19 +25348,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>167.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C38" t="n">
-        <v>150.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D38" t="n">
-        <v>165.311041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E38" t="n">
-        <v>381.9303700722618</v>
+        <v>169.6449844288197</v>
       </c>
       <c r="F38" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G38" t="n">
         <v>415.302737515135</v>
@@ -25417,7 +25417,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y38" t="n">
-        <v>171.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="39">
@@ -25442,13 +25442,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J39" t="n">
         <v>0.7465913262578567</v>
@@ -25475,22 +25475,22 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>106.2867653549601</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>10.94138208097482</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>17.80058714942527</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>251.6949831609196</v>
+        <v>247.1144340662031</v>
       </c>
       <c r="X39" t="n">
         <v>205.7729852034775</v>
@@ -25524,7 +25524,7 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H40" t="n">
-        <v>162.2271725074396</v>
+        <v>29.04020492207155</v>
       </c>
       <c r="I40" t="n">
         <v>155.4504749272583</v>
@@ -25560,7 +25560,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T40" t="n">
-        <v>94.75862184291344</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U40" t="n">
         <v>286.3190293564909</v>
@@ -25591,25 +25591,25 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D41" t="n">
-        <v>354.683041620683</v>
+        <v>141.25877800334</v>
       </c>
       <c r="E41" t="n">
-        <v>381.9303700722618</v>
+        <v>168.5061064549189</v>
       </c>
       <c r="F41" t="n">
-        <v>193.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>202.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H41" t="n">
-        <v>171.2802802553303</v>
+        <v>151.4907107216115</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -25630,7 +25630,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
@@ -25645,7 +25645,7 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V41" t="n">
-        <v>327.7522584701349</v>
+        <v>114.327994852792</v>
       </c>
       <c r="W41" t="n">
         <v>349.240968717413</v>
@@ -25676,19 +25676,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F42" t="n">
-        <v>145.0692123933839</v>
+        <v>127.7936583496243</v>
       </c>
       <c r="G42" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>107.69908777029</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25715,22 +25715,22 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
-        <v>19.80058714942527</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>38.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
         <v>205.6826957773044</v>
@@ -25752,7 +25752,7 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E43" t="n">
-        <v>146.4339626465692</v>
+        <v>99.40903831289552</v>
       </c>
       <c r="F43" t="n">
         <v>145.4210480229312</v>
@@ -25788,7 +25788,7 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q43" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>177.2933913771695</v>
@@ -25812,7 +25812,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y43" t="n">
-        <v>85.39768576672674</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="44">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>350365.0263125472</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>350365.0263125472</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>350365.0263125472</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>352010.690278587</v>
+        <v>351685.0495668242</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>506898.8173466544</v>
+        <v>506909.1411107077</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>506898.8173466544</v>
+        <v>506909.1411107077</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>506898.8173466545</v>
+        <v>506909.1411107076</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>506898.8173466544</v>
+        <v>506909.1411107077</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>488113.7264674625</v>
+        <v>506909.1411107077</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>488113.7264674625</v>
+        <v>506909.1411107078</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>488113.7264674627</v>
+        <v>506909.1411107077</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>486668.7194767555</v>
+        <v>486975.2514232371</v>
       </c>
     </row>
     <row r="16">
@@ -26267,40 +26267,40 @@
         <v>59129.07304229552</v>
       </c>
       <c r="D2" t="n">
-        <v>63177.88319582795</v>
+        <v>59129.07304229552</v>
       </c>
       <c r="E2" t="n">
-        <v>63177.88319582795</v>
+        <v>59129.07304229551</v>
       </c>
       <c r="F2" t="n">
-        <v>63177.88319582795</v>
+        <v>59129.07304229552</v>
       </c>
       <c r="G2" t="n">
-        <v>63474.44484862835</v>
+        <v>63415.76181874349</v>
       </c>
       <c r="H2" t="n">
-        <v>91386.50946835896</v>
+        <v>91388.36989223279</v>
       </c>
       <c r="I2" t="n">
-        <v>91386.50946835896</v>
+        <v>91388.3698922328</v>
       </c>
       <c r="J2" t="n">
-        <v>91386.50946835896</v>
+        <v>91388.36989223283</v>
       </c>
       <c r="K2" t="n">
-        <v>91386.50946835897</v>
+        <v>91388.36989223279</v>
       </c>
       <c r="L2" t="n">
-        <v>88001.28762835896</v>
+        <v>91388.3698922328</v>
       </c>
       <c r="M2" t="n">
-        <v>88001.28762835894</v>
+        <v>91388.3698922328</v>
       </c>
       <c r="N2" t="n">
-        <v>88001.28762835896</v>
+        <v>91388.3698922328</v>
       </c>
       <c r="O2" t="n">
-        <v>87740.88594835896</v>
+        <v>87796.12542771843</v>
       </c>
       <c r="P2" t="n">
         <v>59129.07304229552</v>
@@ -26319,7 +26319,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8076.38</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26328,10 +26328,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>548.1700000000001</v>
+        <v>7562.01207347375</v>
       </c>
       <c r="H3" t="n">
-        <v>57469.317</v>
+        <v>57583.78714233168</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10750.74055314464</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="C4" t="n">
-        <v>10750.74055314464</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="D4" t="n">
-        <v>11524.36744801407</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="E4" t="n">
-        <v>11524.36744801407</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="F4" t="n">
-        <v>11524.36744801407</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="G4" t="n">
-        <v>11581.0330020641</v>
+        <v>13543.27151380256</v>
       </c>
       <c r="H4" t="n">
-        <v>16914.33416026179</v>
+        <v>19775.08488543298</v>
       </c>
       <c r="I4" t="n">
-        <v>16914.33416026178</v>
+        <v>19775.08488543298</v>
       </c>
       <c r="J4" t="n">
-        <v>16914.33416026179</v>
+        <v>19775.08488543298</v>
       </c>
       <c r="K4" t="n">
-        <v>16914.33416026179</v>
+        <v>19775.08488543298</v>
       </c>
       <c r="L4" t="n">
-        <v>16267.50248349411</v>
+        <v>19775.08488543298</v>
       </c>
       <c r="M4" t="n">
-        <v>16267.50248349411</v>
+        <v>19775.08488543298</v>
       </c>
       <c r="N4" t="n">
-        <v>16267.50248349411</v>
+        <v>19775.08488543298</v>
       </c>
       <c r="O4" t="n">
-        <v>16217.74620066583</v>
+        <v>18974.79493644741</v>
       </c>
       <c r="P4" t="n">
-        <v>10750.74055314464</v>
+        <v>12588.27138056849</v>
       </c>
     </row>
     <row r="5">
@@ -26423,40 +26423,40 @@
         <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>35208.4</v>
+        <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1580.8</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1580.8</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1702.4</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="M5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="N5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="O5" t="n">
-        <v>12950.4</v>
+        <v>12976.19522793445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14750.73248915088</v>
+        <v>12913.20166172703</v>
       </c>
       <c r="C6" t="n">
-        <v>14750.73248915088</v>
+        <v>12913.20166172703</v>
       </c>
       <c r="D6" t="n">
-        <v>8368.73574781388</v>
+        <v>12913.20166172703</v>
       </c>
       <c r="E6" t="n">
-        <v>50072.71574781388</v>
+        <v>46540.80166172702</v>
       </c>
       <c r="F6" t="n">
-        <v>50072.71574781388</v>
+        <v>46540.80166172703</v>
       </c>
       <c r="G6" t="n">
-        <v>49642.84184656425</v>
+        <v>40633.00469563995</v>
       </c>
       <c r="H6" t="n">
-        <v>2350.058308097166</v>
+        <v>-624.1708992935455</v>
       </c>
       <c r="I6" t="n">
-        <v>59819.37530809717</v>
+        <v>56959.61624303815</v>
       </c>
       <c r="J6" t="n">
-        <v>59819.37530809717</v>
+        <v>56959.61624303818</v>
       </c>
       <c r="K6" t="n">
-        <v>59819.37530809718</v>
+        <v>56959.61624303814</v>
       </c>
       <c r="L6" t="n">
-        <v>58661.78514486484</v>
+        <v>56959.61624303815</v>
       </c>
       <c r="M6" t="n">
-        <v>58661.78514486483</v>
+        <v>56959.61624303815</v>
       </c>
       <c r="N6" t="n">
-        <v>58661.78514486484</v>
+        <v>56959.61624303815</v>
       </c>
       <c r="O6" t="n">
-        <v>58572.73974769313</v>
+        <v>55845.13526333657</v>
       </c>
       <c r="P6" t="n">
-        <v>48378.33248915088</v>
+        <v>46540.80166172703</v>
       </c>
     </row>
   </sheetData>
@@ -26733,40 +26733,40 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="M4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,16 +26892,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26916,25 +26916,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27191,7 +27191,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27200,10 +27200,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
   </sheetData>
@@ -35088,10 +35088,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -35100,10 +35100,10 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35167,13 +35167,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -35185,7 +35185,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35249,16 +35249,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -35328,19 +35328,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35410,16 +35410,16 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -35486,16 +35486,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -35565,19 +35565,19 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35647,19 +35647,19 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35723,16 +35723,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -35799,22 +35799,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>26.86868686868686</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35881,22 +35881,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>28</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>26.86868686868686</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -35963,10 +35963,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O19" t="n">
         <v>24.58512791403967</v>
@@ -36051,7 +36051,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P20" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36121,19 +36121,19 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>91.05495334897201</v>
+        <v>161.1784674257276</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P21" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q21" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36352,25 +36352,25 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="O24" t="n">
-        <v>169.8645014752148</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P24" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36510,7 +36510,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L26" t="n">
         <v>181.8947995804632</v>
@@ -36519,7 +36519,7 @@
         <v>219.1673002655598</v>
       </c>
       <c r="N26" t="n">
-        <v>207.9338608153932</v>
+        <v>207.9338608153933</v>
       </c>
       <c r="O26" t="n">
         <v>150.7019698410586</v>
@@ -36589,25 +36589,25 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M27" t="n">
-        <v>241</v>
+        <v>43.28534947792188</v>
       </c>
       <c r="N27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P27" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>46.77426503701921</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36756,7 +36756,7 @@
         <v>219.1673002655598</v>
       </c>
       <c r="N29" t="n">
-        <v>207.8772826331474</v>
+        <v>207.9338608153932</v>
       </c>
       <c r="O29" t="n">
         <v>150.7019698410586</v>
@@ -36829,22 +36829,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L30" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>169.8645014752148</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>91.0829537758999</v>
       </c>
       <c r="P30" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36987,13 +36987,13 @@
         <v>104.0555615261842</v>
       </c>
       <c r="L32" t="n">
-        <v>83.05602671428214</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M32" t="n">
-        <v>215</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N32" t="n">
-        <v>207.9338608153932</v>
+        <v>207.9338608153933</v>
       </c>
       <c r="O32" t="n">
         <v>150.7019698410586</v>
@@ -37069,19 +37069,19 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N33" t="n">
-        <v>110.2009720493049</v>
+        <v>91.0829537758999</v>
       </c>
       <c r="O33" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P33" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37227,10 +37227,10 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
-        <v>215</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N35" t="n">
-        <v>109.0950879492122</v>
+        <v>207.9338608153933</v>
       </c>
       <c r="O35" t="n">
         <v>150.7019698410586</v>
@@ -37300,25 +37300,25 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L36" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N36" t="n">
-        <v>206.3131313131313</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O36" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>34.55702612384782</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37464,13 +37464,13 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
-        <v>215</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N38" t="n">
         <v>207.9338608153932</v>
       </c>
       <c r="O38" t="n">
-        <v>51.86319697487763</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P38" t="n">
         <v>90.5657124162131</v>
@@ -37537,25 +37537,25 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M39" t="n">
-        <v>215</v>
+        <v>226.4350751681936</v>
       </c>
       <c r="N39" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P39" t="n">
-        <v>79.6893332749117</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37698,13 +37698,13 @@
         <v>104.0555615261842</v>
       </c>
       <c r="L41" t="n">
-        <v>77.13683479509021</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N41" t="n">
-        <v>207.9338608153932</v>
+        <v>104.4315449177119</v>
       </c>
       <c r="O41" t="n">
         <v>150.7019698410586</v>
@@ -37777,22 +37777,22 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="M42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N42" t="n">
-        <v>213</v>
+        <v>204.8010610469452</v>
       </c>
       <c r="O42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P42" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>19.90557816833244</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
